--- a/results/MVSE/dblp/MVSE_dblp<l10>AllRes_91.33.xlsx
+++ b/results/MVSE/dblp/MVSE_dblp<l10>AllRes_91.33.xlsx
@@ -476,48 +476,48 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>nce_k</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>avg_loss</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>avg_test_mif1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>std_loss</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>std_test_mif1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>config2str</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>walk_hop</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>avg_loss</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>avg_test_mif1</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>std_loss</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>std_test_mif1</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>config2str</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>nce_k</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -582,12 +582,12 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="L3" t="n">
         <v>2</v>
@@ -652,12 +652,12 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -722,12 +722,12 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -792,12 +792,12 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -862,12 +862,12 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -1002,12 +1002,12 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -1072,12 +1072,12 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -1142,12 +1142,12 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -1212,12 +1212,12 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -1282,12 +1282,12 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1306,14 +1306,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NCEK</t>
+          <t>WH</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>128</v>
       </c>
       <c r="G13" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="H13" t="n">
         <v>50</v>
@@ -1329,35 +1329,35 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="N13" t="n">
         <v>90.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="P13" t="n">
-        <v>0.76</v>
+        <v>0.33</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-04_43_39', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-10_20_41', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>8192</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1376,14 +1376,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WH</t>
+          <t>NCEK</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>128</v>
       </c>
       <c r="G14" t="n">
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="H14" t="n">
         <v>50</v>
@@ -1399,30 +1399,30 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>8192</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="N14" t="n">
         <v>90.2</v>
       </c>
       <c r="O14" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="P14" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'walk_hop', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_19-10_20_41', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'WH', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 4096, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 1, 'walk_num': 3, 'weight_decay': 1e-05}</t>
+          <t>{'_interested_conf_list': ['model', 'aug_mode', 'dataset', 'exp_name', 'batch_size', 'train_percentage', 'p_epoch', 'f_epoch', 'ge_mode', 'skip_pretrain', 'model', 'config', 'cl_mode', 'nce_k', 'seed', 'mode'], 'alpha': 0.999, 'aug_mode': 'MPRW', 'batch_size': 128, 'beta1': 0.9, 'beta2': 0.999, 'birth_time': '02_21-04_43_39', 'cl_mode': 'WL_0_0_1', 'clip_norm': 1.0, 'dataset': 'dblp', 'exp_name': 'NCEK', 'f_epoch': 50, 'ge_layer': 2, 'ge_mode': 'mp_spec', 'gnn_model': 'gin', 'lr': 0.005, 'model': 'MVSE', 'mp_list': ['apa', 'apcpa'], 'mv_hidden_size': 48, 'mv_map_layer': 2, 'nce_k': 8192, 'nce_t': 0.07, 'node_emb_dim': 32, 'norm': True, 'num_samples': 2000, 'num_workers': 1, 'p_epoch': 2500, 'positional_embedding_size': 32, 'restart_prob': 0.2, 'seed': 2, 'subg_emb_dim': 64, 'subgraph_size': 128, 'train_mode': 'moco', 'walk_hop': 2, 'walk_num': 3, 'weight_decay': 1e-05}</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -1492,12 +1492,12 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -1562,12 +1562,12 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -1632,12 +1632,12 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -1702,12 +1702,12 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
@@ -1772,12 +1772,12 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="L20" t="n">
         <v>2</v>
@@ -1842,12 +1842,12 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="L21" t="n">
         <v>2</v>
@@ -1912,12 +1912,12 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="L22" t="n">
         <v>2</v>
@@ -1982,12 +1982,12 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="L23" t="n">
         <v>2</v>
@@ -2052,12 +2052,12 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
@@ -2122,12 +2122,12 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="L25" t="n">
         <v>2</v>
@@ -2192,12 +2192,12 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="L26" t="n">
         <v>2</v>
@@ -2262,12 +2262,12 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
@@ -2332,12 +2332,12 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="L28" t="n">
         <v>2</v>
@@ -2402,12 +2402,12 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="L29" t="n">
         <v>2</v>
@@ -2472,12 +2472,12 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
@@ -2542,12 +2542,12 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="L31" t="n">
         <v>2</v>
@@ -2612,12 +2612,12 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="L32" t="n">
         <v>2</v>
@@ -2682,12 +2682,12 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
@@ -2752,12 +2752,12 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="L34" t="n">
         <v>2</v>
@@ -2822,12 +2822,12 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
@@ -2892,12 +2892,12 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
